--- a/17-06-26/Mubeen .xlsx
+++ b/17-06-26/Mubeen .xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE096B0-947C-42F8-A40D-8297E28AA864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE4FDB4-907A-43D9-901C-6391B45C5F8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3384,7 +3384,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3412,7 +3412,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4611,7 +4611,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4639,7 +4639,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5109,12 +5109,10 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>8</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>581.12</v>
+        <v>0</v>
       </c>
       <c r="J19" s="117"/>
       <c r="K19" s="1">
@@ -5123,23 +5121,23 @@
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>46.489600000000003</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>534.63040000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>117.61868800000001</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>16.306227200000002</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>668.5553152</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5167,39 +5165,35 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>6</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>435.84000000000003</v>
-      </c>
-      <c r="J20" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J20" s="117"/>
       <c r="K20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>34.867200000000004</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>400.97280000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>104.194816</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>12.629190400000001</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>517.79680640000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5227,12 +5221,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>7</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>508.48</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -5241,23 +5233,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>40.678400000000003</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>467.80160000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>102.916352</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>14.267948799999999</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>584.98590079999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5285,37 +5277,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>12</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>23.538000000000004</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>430.74540000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>94.763987999999998</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>13.137734700000003</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5445,36 +5435,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1996.2</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>145.57320000000001</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1834.1502</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>419.49384400000002</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>56.341101100000003</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>2309.9851451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5524,7 +5514,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1996.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5545,7 +5535,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>145.57320000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5566,7 +5556,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5588,7 +5578,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1834.1502</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5613,7 +5603,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>419.49384400000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5635,7 +5625,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2253.6440440000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5660,7 +5650,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>56.341101100000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5670,7 +5660,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>2309.9851451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -5842,7 +5832,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5870,7 +5860,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -6508,37 +6498,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>12</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>23.538000000000004</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>430.74540000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>94.763987999999998</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>13.137734700000003</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -6668,36 +6656,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>23.538000000000004</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>430.74540000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>94.763987999999998</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>13.137734700000003</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -6747,7 +6735,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>470.76000000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6768,7 +6756,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>23.538000000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6789,7 +6777,7 @@
       <c r="O30" s="240"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>16.476600000000005</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6811,7 +6799,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>430.74540000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6836,7 +6824,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>94.763987999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -6858,7 +6846,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>525.50938800000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6883,7 +6871,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>13.137734700000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -6893,7 +6881,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -7065,7 +7053,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7093,7 +7081,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8286,7 +8274,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8314,7 +8302,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9507,7 +9495,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9535,7 +9523,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10725,7 +10713,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10753,7 +10741,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11942,7 +11930,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11970,7 +11958,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13159,7 +13147,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13187,7 +13175,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14376,7 +14364,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14404,7 +14392,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18343,7 +18331,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18371,7 +18359,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19560,7 +19548,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19588,7 +19576,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20777,7 +20765,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20805,7 +20793,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21994,7 +21982,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -22022,7 +22010,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23216,7 +23204,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23244,7 +23232,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23541,15 +23529,15 @@
       <c r="G16" s="114"/>
       <c r="H16" s="172">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16</f>
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2728.0499999999997</v>
+        <v>629.54999999999995</v>
       </c>
       <c r="J16" s="172">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="172">
         <f>+'1'!K16+'2'!K16+'4'!K16+'3'!K16+'5'!K16+'6'!K16+'7'!K16+'8'!K16+'9'!K16+'10'!K16</f>
@@ -23557,23 +23545,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>218.244</v>
+        <v>50.363999999999997</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>2509.8059999999996</v>
+        <v>579.18599999999992</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>575.24081999999999</v>
+        <v>127.42091999999998</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>15.425234100000001</v>
+        <v>3.5330345999999997</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>3100.4720540999997</v>
+        <v>710.1399545999999</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23582,7 +23570,7 @@
       </c>
       <c r="U16" s="164">
         <f>+'4'!P35</f>
-        <v>2850.0025873500003</v>
+        <v>0</v>
       </c>
       <c r="XFD16" t="s">
         <v>82</v>
@@ -23615,15 +23603,15 @@
       <c r="G17" s="114"/>
       <c r="H17" s="172">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17</f>
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>3252.6749999999997</v>
+        <v>629.54999999999995</v>
       </c>
       <c r="J17" s="172">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17+'13'!J17+'14'!J17+'15'!J17+'16'!J17+'17'!J17+'18'!J17</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K17" s="172">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
@@ -23631,23 +23619,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>260.214</v>
+        <v>50.363999999999997</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>2992.4609999999998</v>
+        <v>579.18599999999992</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>681.42491999999993</v>
+        <v>127.42091999999998</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>18.3694296</v>
+        <v>3.5330345999999997</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>3692.2553495999996</v>
+        <v>710.1399545999999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23689,15 +23677,15 @@
       <c r="G18" s="114"/>
       <c r="H18" s="172">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18</f>
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>3252.6749999999997</v>
+        <v>629.54999999999995</v>
       </c>
       <c r="J18" s="172">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18+'13'!J18+'14'!J18+'15'!J18+'16'!J18+'17'!J18+'18'!J18</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K18" s="172">
         <f>+'1'!K18+'2'!K18+'4'!K18+'3'!K18+'5'!K18+'6'!K18+'7'!K18+'8'!K18+'9'!K18+'10'!K18</f>
@@ -23705,23 +23693,23 @@
       </c>
       <c r="L18" s="175">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>260.214</v>
+        <v>50.363999999999997</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="2"/>
-        <v>2992.4609999999998</v>
+        <v>579.18599999999992</v>
       </c>
       <c r="N18" s="101">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>704.50842</v>
+        <v>138.96266999999997</v>
       </c>
       <c r="O18" s="101">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>18.4848471</v>
+        <v>3.5907433499999999</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="0"/>
-        <v>3715.4542670999999</v>
+        <v>721.73941334999995</v>
       </c>
       <c r="T18" s="163" t="str">
         <f>+'5'!A5</f>
@@ -23729,7 +23717,7 @@
       </c>
       <c r="U18" s="164">
         <f>+'5'!P35</f>
-        <v>3375.5372160000002</v>
+        <v>3230.1991039999998</v>
       </c>
     </row>
     <row r="19" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23759,11 +23747,11 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19</f>
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>1598.08</v>
+        <v>1016.96</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -23775,23 +23763,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>127.84640000000002</v>
+        <v>81.356800000000007</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>1470.2336</v>
+        <v>935.60320000000002</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>323.451392</v>
+        <v>205.83270400000001</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>28.535897600000006</v>
+        <v>12.229670400000002</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>1822.2208896</v>
+        <v>1153.6655744</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23799,7 +23787,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>7170.9962985000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23829,15 +23817,15 @@
       <c r="G20" s="114"/>
       <c r="H20" s="172">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20</f>
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>3123.52</v>
+        <v>1961.28</v>
       </c>
       <c r="J20" s="172">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K20" s="172">
         <f>+'1'!K20+'2'!K20+'4'!K20+'3'!K20+'5'!K20+'6'!K20+'7'!K20+'8'!K20+'9'!K20+'10'!K20</f>
@@ -23845,23 +23833,23 @@
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>249.88160000000002</v>
+        <v>156.9024</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>2873.6383999999998</v>
+        <v>1804.3776</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>696.123648</v>
+        <v>444.90547199999997</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>34.474653440000004</v>
+        <v>17.76890624</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>3604.2367014399997</v>
+        <v>2267.0519782400002</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23899,15 +23887,15 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>6610.24</v>
+        <v>5375.36</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21+'13'!J21+'14'!J21+'15'!J21+'16'!J21+'17'!J21+'18'!J21</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K21" s="172">
         <f>+'1'!K21+'2'!K21+'4'!K21+'3'!K21+'5'!K21+'6'!K21+'7'!K21+'8'!K21+'9'!K21+'10'!K21</f>
@@ -23915,23 +23903,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>528.81920000000002</v>
+        <v>546.25280000000009</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>6081.4207999999999</v>
+        <v>4829.1071999999995</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>1385.8549759999999</v>
+        <v>1094.365184</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>121.13736960000001</v>
+        <v>99.16812800000001</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>7588.4131455999996</v>
+        <v>6022.6405119999999</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23939,7 +23927,7 @@
       </c>
       <c r="U21" s="164">
         <f>+'8'!P35</f>
-        <v>2309.9851451</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23969,11 +23957,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>941.5200000000001</v>
+        <v>0</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22+'13'!J22+'14'!J22+'15'!J22+'16'!J22+'17'!J22+'18'!J22</f>
@@ -23981,27 +23969,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>32.95320000000001</v>
+        <v>0</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>47.076000000000008</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>861.49080000000004</v>
+        <v>0</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>189.527976</v>
+        <v>0</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>26.275469400000006</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>1077.2942454000001</v>
+        <v>0</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24009,7 +23997,7 @@
       </c>
       <c r="U22" s="164">
         <f>+'9'!P35</f>
-        <v>538.64712270000007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -24159,7 +24147,7 @@
       <c r="B25" s="226"/>
       <c r="C25" s="227">
         <f>H25/40</f>
-        <v>8.9</v>
+        <v>3.7749999999999999</v>
       </c>
       <c r="D25" s="221"/>
       <c r="E25" s="221"/>
@@ -24170,39 +24158,39 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>356</v>
+        <v>151</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>21506.76</v>
+        <v>10242.25</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>32.95320000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>1692.2952</v>
+        <v>935.60400000000004</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>19781.511599999998</v>
+        <v>9306.6459999999988</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>4556.1321520000001</v>
+        <v>2138.90787</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>262.70290084000004</v>
+        <v>139.82351719000002</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>24600.346652839999</v>
+        <v>11585.377387189999</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24332,7 +24320,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>24600.346652839999</v>
+        <v>11585.377387190001</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24365,7 +24353,7 @@
       <c r="O32" s="238"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>21506.76</v>
+        <v>10242.25</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24386,7 +24374,7 @@
       <c r="O33" s="240"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>1692.2952</v>
+        <v>935.60400000000004</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24407,7 +24395,7 @@
       <c r="O34" s="240"/>
       <c r="P34" s="154">
         <f>K25</f>
-        <v>32.95320000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24429,7 +24417,7 @@
       <c r="O35" s="240"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>19781.511599999998</v>
+        <v>9306.6460000000006</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24454,7 +24442,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>4556.1321520000001</v>
+        <v>2138.90787</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24476,7 +24464,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>24337.643751999996</v>
+        <v>11445.55387</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24501,7 +24489,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>608.44109379999998</v>
+        <v>286.13884675000003</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24511,7 +24499,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>24946.084845799996</v>
+        <v>11731.69271675</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24683,7 +24671,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24711,7 +24699,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25912,7 +25900,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25940,7 +25928,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27141,7 +27129,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27169,7 +27157,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28369,7 +28357,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28397,7 +28385,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28751,12 +28739,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>10</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>524.625</v>
+        <v>0</v>
       </c>
       <c r="J17" s="117"/>
       <c r="K17" s="1">
@@ -28765,23 +28751,23 @@
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>482.65499999999997</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>106.1841</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>2.9441954999999997</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>591.78329549999989</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -28813,39 +28799,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="114"/>
-      <c r="H18" s="115">
-        <v>10</v>
-      </c>
+      <c r="H18" s="115"/>
       <c r="I18" s="116">
         <f t="shared" si="2"/>
-        <v>524.625</v>
-      </c>
-      <c r="J18" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" s="117"/>
       <c r="K18" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18" s="105">
         <f t="shared" si="4"/>
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="5"/>
-        <v>482.65499999999997</v>
+        <v>0</v>
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>117.72585000000001</v>
+        <v>0</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="6"/>
-        <v>3.0019042499999999</v>
+        <v>0</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="1"/>
-        <v>603.38275425000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28929,12 +28911,10 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="114"/>
-      <c r="H20" s="115">
-        <v>10</v>
-      </c>
+      <c r="H20" s="115"/>
       <c r="I20" s="116">
         <f t="shared" si="2"/>
-        <v>726.4</v>
+        <v>0</v>
       </c>
       <c r="J20" s="117"/>
       <c r="K20" s="1">
@@ -28943,23 +28923,23 @@
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>58.112000000000002</v>
+        <v>0</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>668.28800000000001</v>
+        <v>0</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>147.02336</v>
+        <v>0</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>4.0765568000000005</v>
+        <v>0</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>819.38791680000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28987,39 +28967,35 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>10</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>726.4</v>
-      </c>
-      <c r="J21" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J21" s="117"/>
       <c r="K21" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>58.112000000000002</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>668.28800000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>163.00415999999998</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>4.1564607999999996</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>835.44862079999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29205,11 +29181,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>2502.0500000000002</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -29218,23 +29194,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>200.16399999999999</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2301.886</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>533.93746999999996</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>14.17911735</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>2850.0025873499999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -29284,7 +29260,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>2502.0500000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29305,7 +29281,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>200.16399999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29348,7 +29324,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2301.8860000000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29373,7 +29349,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>533.93746999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -29395,7 +29371,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2835.8234700000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29420,7 +29396,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>14.179117350000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -29430,7 +29406,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>2850.0025873500003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -29602,7 +29578,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29630,7 +29606,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29935,7 +29911,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="105">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="106">
@@ -29995,7 +29971,7 @@
         <v>0</v>
       </c>
       <c r="L17" s="105">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
         <v>0</v>
       </c>
       <c r="M17" s="118">
@@ -30228,23 +30204,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>232.44800000000001</v>
+        <v>348.67199999999997</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>2673.152</v>
+        <v>2556.9279999999999</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>620.05503999999996</v>
+        <v>594.48575999999991</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>82.330176000000009</v>
+        <v>78.785344000000009</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>3375.5372160000002</v>
+        <v>3230.1991039999998</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30443,23 +30419,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>232.44800000000001</v>
+        <v>348.67199999999997</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2673.152</v>
+        <v>2556.9279999999999</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>620.05503999999996</v>
+        <v>594.48575999999991</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>82.330176000000009</v>
+        <v>78.785344000000009</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>3375.5372160000002</v>
+        <v>3230.1991039999998</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30530,7 +30506,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>232.44800000000001</v>
+        <v>348.67199999999997</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30573,7 +30549,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2673.152</v>
+        <v>2556.9279999999999</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30598,7 +30574,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>620.05503999999996</v>
+        <v>594.48575999999991</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30620,7 +30596,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>3293.2070400000002</v>
+        <v>3151.4137599999999</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30645,7 +30621,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>82.330176000000009</v>
+        <v>78.785344000000009</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30655,7 +30631,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>3375.5372160000002</v>
+        <v>3230.1991039999998</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30827,7 +30803,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46192</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30855,7 +30831,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46191</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -31149,39 +31125,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>40</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>2098.5</v>
-      </c>
-      <c r="J16" s="103">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J16" s="103"/>
       <c r="K16" s="104">
         <f>I16*$K$13</f>
         <v>0</v>
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>167.88</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>1930.62</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>447.81990000000002</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>11.8921995</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>2390.3320994999999</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -31213,39 +31185,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>40</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>2098.5</v>
-      </c>
-      <c r="J17" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>167.88</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>1930.62</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>447.81990000000002</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>11.8921995</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>2390.3320994999999</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -31277,39 +31245,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="114"/>
-      <c r="H18" s="115">
-        <v>40</v>
-      </c>
+      <c r="H18" s="115"/>
       <c r="I18" s="116">
         <f t="shared" si="2"/>
-        <v>2098.5</v>
-      </c>
-      <c r="J18" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J18" s="117"/>
       <c r="K18" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L18" s="105">
         <f t="shared" si="4"/>
-        <v>167.88</v>
+        <v>0</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="5"/>
-        <v>1930.62</v>
+        <v>0</v>
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>447.81990000000002</v>
+        <v>0</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="6"/>
-        <v>11.8921995</v>
+        <v>0</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="1"/>
-        <v>2390.3320994999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31663,11 +31627,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>6295.5</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -31676,23 +31640,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>503.64</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>5791.86</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1343.4597000000001</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>35.676598499999997</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>7170.9962985000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31742,7 +31706,7 @@
       <c r="O28" s="238"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>6295.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31763,7 +31727,7 @@
       <c r="O29" s="240"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>503.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31806,7 +31770,7 @@
       <c r="O31" s="240"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>5791.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31831,7 +31795,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1343.4597000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31853,7 +31817,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>7135.3197</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31878,7 +31842,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>35.676598500000004</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31888,7 +31852,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>7170.9962985000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
